--- a/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/Output.xlsx
+++ b/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/Output.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubRepos\ApsimX\Prototypes\WheatSimpleLeaf\SimpleLeafImplementation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CDABCA1F-AB03-4F60-B068-DAE0BD345F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA305D4D-9F5C-4155-8FFF-143151A20CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{2E361048-D2F4-49DD-B632-E790A115F9B0}"/>
+    <workbookView xWindow="11052" yWindow="0" windowWidth="12024" windowHeight="12336" activeTab="2" xr2:uid="{2E361048-D2F4-49DD-B632-E790A115F9B0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="494">
   <si>
     <t>[Wheat].AboveGround.N</t>
   </si>
@@ -421,6 +422,1104 @@
   </si>
   <si>
     <t>Clock.Today</t>
+  </si>
+  <si>
+    <t>1: 'APS26',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 9: 'APS6',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 15: 'APS14',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 26: 'APS2',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 29: 'GattonRowSpacing',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 32: 'Gatton94',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 44: 'Gatton2009',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 91: 'Gatton2011',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 106: 'Gatton2014',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 254: 'Gatton2014AE',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 403: 'TraitMod2015',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 413: 'TraitMod2016',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 418: 'Goondiwindi2011',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 426: 'Nagwee2012',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 436: 'Bungunya2012',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 445: 'Goondiwindi1996',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 462: 'Miles1996',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 492: 'Emerald1996',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 517: 'Biloela1996',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 547: 'Moree1996',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 564: 'Mer86',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 568: 'Mer73',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 575: 'Cunderdin97',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 615: 'Wongan83',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 624: 'Konya09',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 646: 'Konya11',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 669: 'PalmerstonNorth1989',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 687: 'Lincoln9192',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 694: 'Lincoln1992',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 710: 'Lincoln1994',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 720: 'Lincoln2010',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 727: 'Lincoln2014',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 734: 'Lincoln2015',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 740: 'Leeston2013',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 755: 'Leeston2014',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 763: 'Wakanui2015',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 766: 'Wakanui2016',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 771: 'Wakanui2017',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 774: 'Lincoln2021',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 790: 'Lincoln2023',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 808: 'CPTCultOtane',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 848: 'CPTCultAmarok',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 870: 'CPTCultClaire',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 917: 'CPTCultWakanui',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 922: 'CPTCultBattenSpring',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 935: 'CPTCultBattenWinter',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 948: 'CPTCultYitpi',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 960: 'CPTCultSunco',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 974: 'CPTCultMcCubbin',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 986: 'CPTCultMacKellar',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1000: 'CPTCultJanz',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1013: 'CPTCultLang',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1025: 'CPTCultH45',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1039: 'Wagga1991',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1044: 'Ginninderra1991',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1052: 'Wagga2013',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1056: 'Wagga2014',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1061: 'Mouse',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1081: 'Walpeup2011',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1093: 'Walpeup2012',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1100: 'Minnipa2012',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1110: 'Temora2012',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1119: 'Birchip2011',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1134: 'Tarlee2011',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1151: 'Tamworth1992',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1226: 'Griffith1983',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1236: 'Griffith1984',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1242: 'FAR WAA W20-01a',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1251: 'FAR WAA W20-01b',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1260: 'FAR WAE W21-05',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1264: 'FAR WAE W22-02',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1272: 'FAR DMC W20-03',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1288: 'FAR DMC W20-05',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1292: 'FAR VIC W22-03-2',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1295: 'FAR HYC W17-01-1',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1302: 'FAR HYC W17-01-2',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1308: 'FAR HYC W17-02-1',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1309: 'FAR HYC W17-02-2',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1315: 'FAR TAS W16-01-1',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1321: 'FAR TAS W16-01-2',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1327: 'FAR TAS W16-06',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1363: 'FAR TAS W16-08',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1376: 'FAR HYC W18-02-2',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1379: 'FAR HYC W18-02-2a',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1381: 'FAR HYC W18-08-1',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1385: 'FAR HYC W19-03-1',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1394: 'FAR HYC W19-06-1',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1400: 'FAR TAS W21-03-1',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1406: 'FAR SAC W18-01',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1418: 'FAR SAC W18-02',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1432: 'FAR SAC W19-01',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1444: 'FAR SAC W19-02',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1456: 'FAR SAC W20-03-2',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1468: 'FAR SAC W20-05-1',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1472: 'FAR SAC W22-03-2',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1476: 'FAR RRC W21-03',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1485: 'FAR RRC W22-03',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1496: 'MaricopaFACE92_93',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1499: 'MaricopaFACE93_94',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1504: 'MaricopaFACE95_96',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1508: 'MaricopaFACE96_97',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1516: 'Jamma',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1521: 'LaTrobeCE',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1797: 'PalmerstonNorthCE',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2004: 'LincolnCE',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2029: 'WaggaWagga',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2541: 'Callington',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 3053: 'Dale',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 3565: 'YanYean',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4076: 'SGEHEAT_13GEHEAT-1',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4083: 'SGEHEAT_13GEHEAT-2',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4086: '14SSOW-1',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4123: '14SSOW-2',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4158: '14SSOW-4',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4190: '14SSOW-5',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4222: '12JuneeJames-1-100',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4225: '12JuneeJames-1-50',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4226: '12JuneeJames-2-100',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4228: '12JuneeJames-3-100',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4229: '12JuneeJames-2-50',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4232: '12JuneeJames-4-100',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4234: 'BCVT_Badgingarra_2005-05-26',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4235: 'BCVT_Badgingarra_2005-05-28',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4236: 'BCVT_Ardingly_1992-06-19',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4237: 'BCVT_Badjaling_2003-05-30',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4238: 'BCVT_Chapman_1992-06-23',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4239: 'BCVT_Chapman_1994-06-10',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4240: 'BCVT_Chapman_1992-06-24',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4241: 'BCVT_Gairdner_River_2004-06-09',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4242: 'BCVT_Georgina_1992-06-26',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4243: 'BCVT_Konnongorring_1997-06-27',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4244: 'BCVT_Konnongorring_1997-06-13',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4245: 'BCVT_Kunjin_2005-05-26',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4246: 'BCVT_Kumarl_1999-05-22',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4247: 'BCVT_Merredin_1995-05-30',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4248: 'BCVT_Merredin_1996-07-02',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4249: 'BCVT_Meckering_2003-06-04',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4250: 'BCVT_Merredin_1996-06-25',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4251: 'BCVT_Merredin_1998-06-19',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4252: 'BCVT_Merredin_2000-06-19',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4253: 'BCVT_Merredin_2002-06-10',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4254: 'BCVT_Merredin_2003-06-06',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4256: 'BCVT_Mt_Madden_1994-06-13',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4257: 'BCVT_Mukinbudin_2000-06-13',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4258: 'BCVT_Mullewa_1993-06-04',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4259: 'BCVT_Mullewa_2004-05-28',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4260: 'BCVT_Scaddan_1999-05-25',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4261: 'BCVT_Munglinup_1994-06-08',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4262: 'BCVT_Speddingup_2001-05-30',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4263: 'BCVT_Tammin_1999-06-09',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4264: 'BCVT_Wongan_Hills_1998-06-09',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4265: 'BCVT_Wannamal_1992-06-25',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4266: 'BCVT_Wongan_Hills_2001-06-11',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4267: 'BCVT_Wongan_Hills_2002-06-09',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4268: 'BTOS_2008GE1',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4271: 'BTOS_2008GE2',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4281: 'BTOS_2008GE3',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4289: 'BTOS_2008GE4',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4300: 'BTOS_2008KA1',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4302: 'BTOS_2008KA2',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4303: 'BTOS_2008KA3',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4308: 'BTOS_2008KA4',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4319: 'BTOS_2008NM3',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4326: 'BTOS_2008NM2',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4333: 'BTOS_2008NM4',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4344: 'BTOS_2009GE1',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4350: 'BTOS_2009GE3',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4353: 'BTOS_2009GE2',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4360: 'BTOS_2009GE4',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4374: 'BTOS_2009KA3',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4376: 'BYIE_08HIR',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4381: 'BYIE_08KA',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4388: 'BYIE_08NB',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4400: 'BYIE_08RS',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4412: 'BYIE_08WH',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4427: 'BYIE_09ER',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4438: 'BYIE_09GN',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4451: 'BYIE_09HIR',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4453: 'BYIE_09KA',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4460: 'BYIE_09MDL',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4474: 'BYIE_09RS',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4479: 'BYIE_09WH',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4492: 'PTOS_10Kairi-1',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4501: 'PTOS_10Kairi-2',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4506: 'PTOS_10Kairi-3',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4514: 'PTOS_10Kairi-4',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4523: 'PTOS_10Kairi-5',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4531: 'PTOS_10Mackay-1',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4540: 'PTOS_10Mackay-2',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4547: 'PTOS_10Mackay-3',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4555: 'PTOS_10Mackay-4',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4560: 'PTOS_10Mackay-5',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4570: 'HAGT_09Roseworthy-1',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4573: 'HAGT_09Roseworthy-2',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4574: 'HAGT_09Roseworthy-3',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4575: 'HAGT_09Roseworthy-4',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4579: 'HAGT_09Roseworthy-5',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4583: '17CuryoMESW-TOS1',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4588: '17CuryoMESW-TOS2',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4592: '17CuryoMESW-TOS3',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4598: '17CuryoMESW-TOS4',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4601: '17HartMESW-TOS1',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4608: '17HartMESW-TOS2',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4612: '17HartMESW-TOS3',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4618: '17HartMESW-TOS4',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4622: '17LoxtonMESW-TOS1',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4627: '17LoxtonMESW-TOS2',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4633: '17LoxtonMESW-TOS3',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4637: '17LoxtonMESW-TOS4',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4639: '17MilduraMESW-TOS1',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4648: '17MilduraMESW-TOS2',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4653: '17MilduraMESW-TOS3',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4658: '17MilduraMESW-TOS4',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4663: '17MinnipaMESW-TOS1',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4667: '17MinnipaMESW-TOS2',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4670: '17MinnipaMESW-TOS3',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4674: '17MinnipaMESW-TOS4',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4679: '18HartMESW-TOS1',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4683: '18HartMESW-TOS2',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4689: '18HartMESW-TOS3',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4694: '18HartMESW-TOS4',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4699: '18LoxtonMESW-TOS1',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4704: '18LoxtonMESW-TOS2',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4709: '18LoxtonMESW-TOS3',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4713: '18LoxtonMESW-TOS4',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4719: '18MilduraMESW-TOS1',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4724: '18MilduraMESW-TOS2',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4728: '18MilduraMESW-TOS3',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4733: '18MilduraMESW-TOS4',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4739: 'Inverleigh2013-TOS1',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4740: 'Inverleigh2013-TOS2',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4741: 'Temora2015-TOS1',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4748: 'Temora2015-TOS2',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4755: 'Temora2015-TOS3',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4761: 'Temora2015-TOS4',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4768: 'Brookstead2015-TOS1',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4772: 'Brookstead2015-TOS2',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4775: 'Brookstead2015-TOS3',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4777: 'Emerald2015-TOS1',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4781: 'Emerald2015-TOS2',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4783: 'Emerald2015-TOS3',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4787: 'Minnipa2015-TOS1',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4790: 'Minnipa2015-TOS2',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4795: 'Minnipa2015-TOS3',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4798: 'Temora2016-TOS4',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4801: 'Hart2015-TOS1',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4803: 'Hart2015-TOS2',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4804: 'Hart2015-TOS3',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4807: 'Inverleigh2013-TOS4',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4808: 'Inverleigh2013-TOS3',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4809: 'WaggaWagga2020',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 5313: 'Urrbrae2020',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 5814: 'Dale2020',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 6320: 'YanYean2020',</t>
+  </si>
+  <si>
+    <t>APS26NRate160WaterWet</t>
+  </si>
+  <si>
+    <t>APS6Base</t>
+  </si>
+  <si>
+    <t>APS14StubbleBareNRate0</t>
+  </si>
+  <si>
+    <t>APS2Base</t>
+  </si>
+  <si>
+    <t>RowSpace</t>
+  </si>
+  <si>
+    <t>Gatton94Base</t>
+  </si>
+  <si>
+    <t>Gatton2009Base</t>
+  </si>
+  <si>
+    <t>Gatton2011Base</t>
+  </si>
+  <si>
+    <t>14SOWbase</t>
+  </si>
+  <si>
+    <t>14VPbase</t>
+  </si>
+  <si>
+    <t>15TraitModbase</t>
+  </si>
+  <si>
+    <t>16TraitModbase</t>
+  </si>
+  <si>
+    <t>Goondiwindi2011Base</t>
+  </si>
+  <si>
+    <t>Nangwee2012Base</t>
+  </si>
+  <si>
+    <t>Bungunya2012Base</t>
+  </si>
+  <si>
+    <t>Goondiwindi1996Base</t>
+  </si>
+  <si>
+    <t>Miles1996Base</t>
+  </si>
+  <si>
+    <t>Emerald1996Base</t>
+  </si>
+  <si>
+    <t>Biloela1996Base</t>
+  </si>
+  <si>
+    <t>Moree1996Base</t>
+  </si>
+  <si>
+    <t>Mer86Base</t>
+  </si>
+  <si>
+    <t>Mer73Base</t>
+  </si>
+  <si>
+    <t>Cunderdin97Base</t>
+  </si>
+  <si>
+    <t>WonganBase</t>
+  </si>
+  <si>
+    <t>Konya09</t>
+  </si>
+  <si>
+    <t>Konya11</t>
+  </si>
+  <si>
+    <t>PalmerstonNorth1989Base</t>
+  </si>
+  <si>
+    <t>LincolnBase</t>
+  </si>
+  <si>
+    <t>SDtrialBase</t>
+  </si>
+  <si>
+    <t>Lincoln1994Base</t>
+  </si>
+  <si>
+    <t>Baxters</t>
+  </si>
+  <si>
+    <t>Rainshelter2013</t>
+  </si>
+  <si>
+    <t>Lincoln2015</t>
+  </si>
+  <si>
+    <t>Leeston2013Base</t>
+  </si>
+  <si>
+    <t>Wakanui2014Base</t>
+  </si>
+  <si>
+    <t>Wakanui2015Base</t>
+  </si>
+  <si>
+    <t>Wakanui2016Base</t>
+  </si>
+  <si>
+    <t>Wakanui2017Base</t>
+  </si>
+  <si>
+    <t>Wheat</t>
+  </si>
+  <si>
+    <t>Lincoln23Base</t>
+  </si>
+  <si>
+    <t>LincolnCPTOtane</t>
+  </si>
+  <si>
+    <t>LincolnCPTClaire</t>
+  </si>
+  <si>
+    <t>Wagga91Base</t>
+  </si>
+  <si>
+    <t>Ginninderra91Base</t>
+  </si>
+  <si>
+    <t>Ketema2013</t>
+  </si>
+  <si>
+    <t>Ketema2014</t>
+  </si>
+  <si>
+    <t>YarrabahCreek</t>
+  </si>
+  <si>
+    <t>MouseBase</t>
+  </si>
+  <si>
+    <t>Walpeup2011Base</t>
+  </si>
+  <si>
+    <t>Walpeup2012Base</t>
+  </si>
+  <si>
+    <t>Minnipa2012Base</t>
+  </si>
+  <si>
+    <t>Temora2012Base</t>
+  </si>
+  <si>
+    <t>Birchip2011Base</t>
+  </si>
+  <si>
+    <t>Tarlee2011Base</t>
+  </si>
+  <si>
+    <t>Tamworth1992Base</t>
+  </si>
+  <si>
+    <t>Griffith1983Base</t>
+  </si>
+  <si>
+    <t>Griffith1984Base</t>
+  </si>
+  <si>
+    <t>FAR WAA W20-01abase</t>
+  </si>
+  <si>
+    <t>FAR WAA W20-01bbase</t>
+  </si>
+  <si>
+    <t>FAR WAE W21-05base</t>
+  </si>
+  <si>
+    <t>FAR WAE W22-02base</t>
+  </si>
+  <si>
+    <t>FAR DMC W20-03base</t>
+  </si>
+  <si>
+    <t>FAR DMC W20-05base</t>
+  </si>
+  <si>
+    <t>FAR VIC W22-03-2base</t>
+  </si>
+  <si>
+    <t>FAR HYC W17-01-1base</t>
+  </si>
+  <si>
+    <t>FAR HYC W17-01-2base</t>
+  </si>
+  <si>
+    <t>FAR HYC W17-02-1base</t>
+  </si>
+  <si>
+    <t>FAR HYC W17-02-2base</t>
+  </si>
+  <si>
+    <t>FAR TAS W16-01-1base</t>
+  </si>
+  <si>
+    <t>FAR TAS W16-01-2base</t>
+  </si>
+  <si>
+    <t>FAR TAS W16-06base</t>
+  </si>
+  <si>
+    <t>FAR TAS W16-08base</t>
+  </si>
+  <si>
+    <t>FAR HYC W18-02-2base</t>
+  </si>
+  <si>
+    <t>FAR HYC W18-02-2abase</t>
+  </si>
+  <si>
+    <t>FAR HYC W18-08-1base</t>
+  </si>
+  <si>
+    <t>FAR HYC W19-03-1base</t>
+  </si>
+  <si>
+    <t>FAR HYC W19-06-1base</t>
+  </si>
+  <si>
+    <t>FAR TAS W21-03-1base</t>
+  </si>
+  <si>
+    <t>FAR SAC W18-01base</t>
+  </si>
+  <si>
+    <t>FAR SAC W18-02base</t>
+  </si>
+  <si>
+    <t>FAR SAC W19-01base</t>
+  </si>
+  <si>
+    <t>FAR SAC W19-02base</t>
+  </si>
+  <si>
+    <t>FAR SAC W20-03-2base</t>
+  </si>
+  <si>
+    <t>FAR SAC W20-05-1base</t>
+  </si>
+  <si>
+    <t>FAR SAC W22-03-2base</t>
+  </si>
+  <si>
+    <t>FAR RRC W21-03base</t>
+  </si>
+  <si>
+    <t>FAR RRC W22-03base</t>
+  </si>
+  <si>
+    <t>Lonzee04</t>
+  </si>
+  <si>
+    <t>Lonzee06</t>
+  </si>
+  <si>
+    <t>Lonzee08</t>
+  </si>
+  <si>
+    <t>Maricopa92_93</t>
+  </si>
+  <si>
+    <t>Maricopa93_94</t>
+  </si>
+  <si>
+    <t>Maricopa95_96</t>
+  </si>
+  <si>
+    <t>Maricopa96_97</t>
+  </si>
+  <si>
+    <t>Yucheng02</t>
+  </si>
+  <si>
+    <t>Yucheng03</t>
+  </si>
+  <si>
+    <t>Yucheng04</t>
+  </si>
+  <si>
+    <t>Gorgan05</t>
+  </si>
+  <si>
+    <t>Jamma</t>
+  </si>
+  <si>
+    <t>CEBase</t>
+  </si>
+  <si>
+    <t>PNGrowthRooms</t>
+  </si>
+  <si>
+    <t>LincolnUniBiotron</t>
+  </si>
+  <si>
+    <t>WaggaWagga2019Base</t>
+  </si>
+  <si>
+    <t>Callington2019Base</t>
+  </si>
+  <si>
+    <t>Dale2019Base</t>
+  </si>
+  <si>
+    <t>YanYean2019Base</t>
+  </si>
+  <si>
+    <t>WaggaWagga2020Base</t>
+  </si>
+  <si>
+    <t>Urrbrae2020Base</t>
+  </si>
+  <si>
+    <t>Dale2020Base</t>
+  </si>
+  <si>
+    <t>YanYean2020Base</t>
+  </si>
+  <si>
+    <t>With Output</t>
+  </si>
+  <si>
+    <t>With data</t>
   </si>
 </sst>
 </file>
@@ -811,9 +1910,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{195AC7C7-C7BE-47FF-B9F3-565B7EB397E8}">
   <dimension ref="A1:A35"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="77.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="77.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
@@ -999,10 +2098,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E00C46A0-1807-49DA-AF97-F687999CE71E}">
   <dimension ref="A2:H94"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="80" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="77.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="77.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:8">
@@ -1987,4 +3086,1663 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F573AB7-3C61-4B20-B64E-112EDDA16D12}">
+  <dimension ref="A1:E263"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="36.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>493</v>
+      </c>
+      <c r="D1" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D45" s="1"/>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D46" s="1"/>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D47" s="1"/>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D48" s="1"/>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="D49" s="1"/>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D50" s="1"/>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D51" s="1"/>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D52" s="1"/>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D53" s="1"/>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D54" s="1"/>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="1"/>
+      <c r="D59" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" s="1"/>
+      <c r="D100" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" s="1"/>
+      <c r="D101" s="1" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" s="1"/>
+      <c r="D102" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="1"/>
+      <c r="D107" s="1" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" s="1"/>
+      <c r="D108" s="1" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" s="1"/>
+      <c r="D109" s="1" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" s="1"/>
+      <c r="D110" s="1" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E120" s="1"/>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="E121" s="1"/>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E122" s="1"/>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="E123" s="1"/>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
+      <c r="A128" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" s="1" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" s="1" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" s="1" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" s="1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" s="1" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170" s="1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172" s="1" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180" s="1" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182" s="1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186" s="1" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187" s="1" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188" s="1" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189" s="1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190" s="1" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192" s="1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1">
+      <c r="A193" s="1" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195" s="1" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1">
+      <c r="A196" s="1" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197" s="1" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1">
+      <c r="A198" s="1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1">
+      <c r="A199" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1">
+      <c r="A200" s="1" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1">
+      <c r="A201" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1">
+      <c r="A202" s="1" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1">
+      <c r="A203" s="1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1">
+      <c r="A208" s="1" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209" s="1" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1">
+      <c r="A210" s="1" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211" s="1" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1">
+      <c r="A212" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213" s="1" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214" s="1" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1">
+      <c r="A215" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216" s="1" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217" s="1" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218" s="1" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219" s="1" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1">
+      <c r="A221" s="1" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1">
+      <c r="A222" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1">
+      <c r="A223" s="1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225" s="1" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226" s="1" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228" s="1" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1">
+      <c r="A229" s="1" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1">
+      <c r="A230" s="1" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231" s="1" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232" s="1" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1">
+      <c r="A233" s="1" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236" s="1" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240" s="1" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241" s="1" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243" s="1" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1">
+      <c r="A244" s="1" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1">
+      <c r="A245" s="1" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1">
+      <c r="A246" s="1" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1">
+      <c r="A247" s="1" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1">
+      <c r="A248" s="1" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1">
+      <c r="A249" s="1" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1">
+      <c r="A250" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1">
+      <c r="A251" s="1" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1">
+      <c r="A252" s="1" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1">
+      <c r="A253" s="1" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1">
+      <c r="A254" s="1" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1">
+      <c r="A255" s="1" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1">
+      <c r="A256" s="1" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4">
+      <c r="A257" s="1" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4">
+      <c r="A258" s="1" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4">
+      <c r="A259" s="1" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4">
+      <c r="A260" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D260" s="1" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4">
+      <c r="A261" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D261" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4">
+      <c r="A262" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D262" s="1" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4">
+      <c r="A263" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D263" s="1" t="s">
+        <v>491</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>